--- a/tests/BrandnameMT test/Brandnamedata.xlsx
+++ b/tests/BrandnameMT test/Brandnamedata.xlsx
@@ -2,41 +2,47 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sarvam API\tests\BrandnameMT test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBBCD34-221B-4D83-A420-CEF4D25E12AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C011539-8D16-4B8D-8612-23CF8E99990F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
-  <si>
-    <t xml:space="preserve">Sno </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="62">
+  <si>
+    <t>Sno</t>
   </si>
   <si>
     <t>text</t>
   </si>
   <si>
-    <t xml:space="preserve">output text </t>
+    <t>Language</t>
   </si>
   <si>
     <t>BrandName</t>
   </si>
   <si>
+    <t>NotContains</t>
+  </si>
+  <si>
     <t>The Citroen C3 has a seating capacity of five people, making it perfect for small families or groups.</t>
   </si>
   <si>
+    <t>Hindi</t>
+  </si>
+  <si>
     <t>Citroen C3</t>
   </si>
   <si>
@@ -53,16 +59,13 @@
   </si>
   <si>
     <t>The Citroen C3 packs features aimed at safety, comfort, and connectivity.</t>
-  </si>
-  <si>
-    <t>Citroen C3 Feel Monotone</t>
   </si>
   <si>
     <t xml:space="preserve">	
 Citroen C3 Feel Monotone</t>
   </si>
   <si>
-    <t>NotContains</t>
+    <t>Citroen C3 Feel Monotone</t>
   </si>
   <si>
     <t>“Hello,” she said, ‘the code’s formatting is completely broken.’</t>
@@ -89,15 +92,15 @@
     <t>L'Oréal,Élysées</t>
   </si>
   <si>
+    <t>Get the benefit amount to the extent of the value of beneﬁts</t>
+  </si>
+  <si>
     <t xml:space="preserve">लाभों </t>
   </si>
   <si>
     <t>ﬁT</t>
   </si>
   <si>
-    <t>Get the benefit amount to the extent of the value of beneﬁts</t>
-  </si>
-  <si>
     <t>In comparing the Nothing Ear (&lt;n1&gt;) with the Nothing Ear (&lt;n2&gt;) earbuds, both models offer outstanding audio quality and cutting-edge features in Nothing's signature transparent design</t>
   </si>
   <si>
@@ -153,13 +156,64 @@
   </si>
   <si>
     <t>(ckycrr)</t>
+  </si>
+  <si>
+    <t>Feltron 80 cm (32 inch) HD Ready Smart LED TV (FT-3209SFL) img6.</t>
+  </si>
+  <si>
+    <t>Feltron</t>
+  </si>
+  <si>
+    <t>IFB DeepClean® 10 kg Front Load Washing Machine with Oxyjet®</t>
+  </si>
+  <si>
+    <t>Oxyjet®</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ऑक्सीजन </t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Step 3:&lt;/strong&gt; Log in using your registered mobile number, EPIC number, and password.</t>
+  </si>
+  <si>
+    <t>ईमेल नंबर</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, voter ID card can be downloaded online in Gujarat through the NVSP portal or Voter Helpline App using EPIC details and OTP verification. </t>
+  </si>
+  <si>
+    <t>ईपीएफ विवरण</t>
+  </si>
+  <si>
+    <t>Credit score of 720+</t>
+  </si>
+  <si>
+    <t>720+</t>
+  </si>
+  <si>
+    <t>Credit score of &lt;n1&gt;+</t>
+  </si>
+  <si>
+    <t>&lt;n1&gt;+</t>
+  </si>
+  <si>
+    <t>Tamil</t>
+  </si>
+  <si>
+    <t>Malayalam</t>
+  </si>
+  <si>
+    <t>Telugu</t>
+  </si>
+  <si>
+    <t>Marathi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,16 +224,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,21 +247,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -239,44 +278,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -303,32 +342,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -355,24 +376,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -384,259 +387,304 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="24.81640625" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="58" customHeight="1" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>8</v>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>10</v>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
       <c r="D6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="58" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>4</v>
+      <c r="C8" t="s">
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>10</v>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -644,182 +692,2042 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>18</v>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>6</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>20</v>
+      <c r="B14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" t="s">
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="D15" t="s">
-        <v>22</v>
-      </c>
       <c r="E15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
+      <c r="B16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
       </c>
       <c r="D16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>27</v>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>29</v>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>31</v>
+      <c r="B19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" t="s">
+        <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>33</v>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>35</v>
+      <c r="B21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>6</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="58" x14ac:dyDescent="0.35">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="B22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="C22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>38</v>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" t="s">
+        <v>6</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>40</v>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>6</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>1</v>
+      </c>
+      <c r="B33" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" t="s">
+        <v>58</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>2</v>
+      </c>
+      <c r="B34" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" t="s">
+        <v>58</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" t="s">
+        <v>58</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>8</v>
+      </c>
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>13</v>
+      </c>
+      <c r="B45" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>58</v>
+      </c>
+      <c r="D47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+      <c r="C49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>18</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>58</v>
+      </c>
+      <c r="D50" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>19</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" t="s">
+        <v>58</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>21</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>22</v>
+      </c>
+      <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
+        <v>58</v>
+      </c>
+      <c r="D54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>23</v>
+      </c>
+      <c r="B55" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" t="s">
         <v>42</v>
       </c>
-      <c r="D25" t="s">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>24</v>
+      </c>
+      <c r="B56" t="s">
         <v>43</v>
       </c>
+      <c r="C56" t="s">
+        <v>58</v>
+      </c>
+      <c r="D56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>45</v>
+      </c>
+      <c r="C57" t="s">
+        <v>58</v>
+      </c>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>26</v>
+      </c>
+      <c r="B58" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" t="s">
+        <v>58</v>
+      </c>
+      <c r="D58" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>58</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>28</v>
+      </c>
+      <c r="B60" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>29</v>
+      </c>
+      <c r="B61" t="s">
+        <v>52</v>
+      </c>
+      <c r="C61" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>30</v>
+      </c>
+      <c r="B62" t="s">
+        <v>54</v>
+      </c>
+      <c r="C62" t="s">
+        <v>58</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>31</v>
+      </c>
+      <c r="B63" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" t="s">
+        <v>58</v>
+      </c>
+      <c r="D63" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" t="s">
+        <v>59</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>59</v>
+      </c>
+      <c r="D65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" t="s">
+        <v>59</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>59</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>59</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>8</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>59</v>
+      </c>
+      <c r="D71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" t="s">
+        <v>59</v>
+      </c>
+      <c r="D72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>11</v>
+      </c>
+      <c r="B74" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>19</v>
+      </c>
+      <c r="C75" t="s">
+        <v>59</v>
+      </c>
+      <c r="D75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>13</v>
+      </c>
+      <c r="B76" t="s">
+        <v>21</v>
+      </c>
+      <c r="C76" t="s">
+        <v>59</v>
+      </c>
+      <c r="D76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" t="s">
+        <v>59</v>
+      </c>
+      <c r="E77" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>59</v>
+      </c>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>16</v>
+      </c>
+      <c r="B79" t="s">
+        <v>28</v>
+      </c>
+      <c r="C79" t="s">
+        <v>59</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>17</v>
+      </c>
+      <c r="B80" t="s">
+        <v>30</v>
+      </c>
+      <c r="C80" t="s">
+        <v>59</v>
+      </c>
+      <c r="D80" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>18</v>
+      </c>
+      <c r="B81" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" t="s">
+        <v>59</v>
+      </c>
+      <c r="D81" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>19</v>
+      </c>
+      <c r="B82" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" t="s">
+        <v>59</v>
+      </c>
+      <c r="D82" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>20</v>
+      </c>
+      <c r="B83" t="s">
+        <v>36</v>
+      </c>
+      <c r="C83" t="s">
+        <v>59</v>
+      </c>
+      <c r="D83" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>21</v>
+      </c>
+      <c r="B84" t="s">
+        <v>37</v>
+      </c>
+      <c r="C84" t="s">
+        <v>59</v>
+      </c>
+      <c r="E84" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>22</v>
+      </c>
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85" t="s">
+        <v>59</v>
+      </c>
+      <c r="D85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>23</v>
+      </c>
+      <c r="B86" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" t="s">
+        <v>59</v>
+      </c>
+      <c r="D86" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>24</v>
+      </c>
+      <c r="B87" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" t="s">
+        <v>59</v>
+      </c>
+      <c r="D87" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" t="s">
+        <v>59</v>
+      </c>
+      <c r="D88" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>26</v>
+      </c>
+      <c r="B89" t="s">
+        <v>47</v>
+      </c>
+      <c r="C89" t="s">
+        <v>59</v>
+      </c>
+      <c r="D89" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>27</v>
+      </c>
+      <c r="B90" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>28</v>
+      </c>
+      <c r="B91" t="s">
+        <v>50</v>
+      </c>
+      <c r="C91" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>29</v>
+      </c>
+      <c r="B92" t="s">
+        <v>52</v>
+      </c>
+      <c r="C92" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>30</v>
+      </c>
+      <c r="B93" t="s">
+        <v>54</v>
+      </c>
+      <c r="C93" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>31</v>
+      </c>
+      <c r="B94" t="s">
+        <v>56</v>
+      </c>
+      <c r="C94" t="s">
+        <v>59</v>
+      </c>
+      <c r="D94" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>1</v>
+      </c>
+      <c r="B95" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>60</v>
+      </c>
+      <c r="D95" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" t="s">
+        <v>60</v>
+      </c>
+      <c r="D96" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>3</v>
+      </c>
+      <c r="B97" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" t="s">
+        <v>60</v>
+      </c>
+      <c r="D97" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" t="s">
+        <v>60</v>
+      </c>
+      <c r="D98" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>6</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>8</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>60</v>
+      </c>
+      <c r="D102" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>9</v>
+      </c>
+      <c r="B103" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" t="s">
+        <v>60</v>
+      </c>
+      <c r="D103" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>10</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>60</v>
+      </c>
+      <c r="E104" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>17</v>
+      </c>
+      <c r="C105" t="s">
+        <v>60</v>
+      </c>
+      <c r="D105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" t="s">
+        <v>60</v>
+      </c>
+      <c r="D106" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>13</v>
+      </c>
+      <c r="B107" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" t="s">
+        <v>60</v>
+      </c>
+      <c r="D107" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>14</v>
+      </c>
+      <c r="B108" t="s">
+        <v>23</v>
+      </c>
+      <c r="C108" t="s">
+        <v>60</v>
+      </c>
+      <c r="E108" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>26</v>
+      </c>
+      <c r="C109" t="s">
+        <v>60</v>
+      </c>
+      <c r="D109" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>16</v>
+      </c>
+      <c r="B110" t="s">
+        <v>28</v>
+      </c>
+      <c r="C110" t="s">
+        <v>60</v>
+      </c>
+      <c r="E110" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>17</v>
+      </c>
+      <c r="B111" t="s">
+        <v>30</v>
+      </c>
+      <c r="C111" t="s">
+        <v>60</v>
+      </c>
+      <c r="D111" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>18</v>
+      </c>
+      <c r="B112" t="s">
+        <v>32</v>
+      </c>
+      <c r="C112" t="s">
+        <v>60</v>
+      </c>
+      <c r="D112" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>19</v>
+      </c>
+      <c r="B113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C113" t="s">
+        <v>60</v>
+      </c>
+      <c r="D113" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>20</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" t="s">
+        <v>60</v>
+      </c>
+      <c r="D114" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>21</v>
+      </c>
+      <c r="B115" t="s">
+        <v>37</v>
+      </c>
+      <c r="C115" t="s">
+        <v>60</v>
+      </c>
+      <c r="E115" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>22</v>
+      </c>
+      <c r="B116" t="s">
+        <v>39</v>
+      </c>
+      <c r="C116" t="s">
+        <v>60</v>
+      </c>
+      <c r="D116" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>23</v>
+      </c>
+      <c r="B117" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" t="s">
+        <v>60</v>
+      </c>
+      <c r="D117" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>24</v>
+      </c>
+      <c r="B118" t="s">
+        <v>43</v>
+      </c>
+      <c r="C118" t="s">
+        <v>60</v>
+      </c>
+      <c r="D118" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119" t="s">
+        <v>60</v>
+      </c>
+      <c r="D119" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>26</v>
+      </c>
+      <c r="B120" t="s">
+        <v>47</v>
+      </c>
+      <c r="C120" t="s">
+        <v>60</v>
+      </c>
+      <c r="D120" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>27</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121" t="s">
+        <v>60</v>
+      </c>
+      <c r="D121" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>50</v>
+      </c>
+      <c r="C122" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>29</v>
+      </c>
+      <c r="B123" t="s">
+        <v>52</v>
+      </c>
+      <c r="C123" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>30</v>
+      </c>
+      <c r="B124" t="s">
+        <v>54</v>
+      </c>
+      <c r="C124" t="s">
+        <v>60</v>
+      </c>
+      <c r="D124" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>31</v>
+      </c>
+      <c r="B125" t="s">
+        <v>56</v>
+      </c>
+      <c r="C125" t="s">
+        <v>60</v>
+      </c>
+      <c r="D125" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" t="s">
+        <v>61</v>
+      </c>
+      <c r="D126" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>2</v>
+      </c>
+      <c r="B127" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" t="s">
+        <v>61</v>
+      </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>3</v>
+      </c>
+      <c r="B128" t="s">
+        <v>10</v>
+      </c>
+      <c r="C128" t="s">
+        <v>61</v>
+      </c>
+      <c r="D128" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>4</v>
+      </c>
+      <c r="B129" t="s">
+        <v>11</v>
+      </c>
+      <c r="C129" t="s">
+        <v>61</v>
+      </c>
+      <c r="D129" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
+        <v>61</v>
+      </c>
+      <c r="D130" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>6</v>
+      </c>
+      <c r="B131" t="s">
+        <v>13</v>
+      </c>
+      <c r="C131" t="s">
+        <v>61</v>
+      </c>
+      <c r="D131" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" t="s">
+        <v>61</v>
+      </c>
+      <c r="D132" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>8</v>
+      </c>
+      <c r="B133" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133" t="s">
+        <v>61</v>
+      </c>
+      <c r="D133" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>9</v>
+      </c>
+      <c r="B134" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" t="s">
+        <v>61</v>
+      </c>
+      <c r="D134" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>10</v>
+      </c>
+      <c r="B135" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" t="s">
+        <v>61</v>
+      </c>
+      <c r="E135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>11</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>61</v>
+      </c>
+      <c r="D136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>19</v>
+      </c>
+      <c r="C137" t="s">
+        <v>61</v>
+      </c>
+      <c r="D137" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>13</v>
+      </c>
+      <c r="B138" t="s">
+        <v>21</v>
+      </c>
+      <c r="C138" t="s">
+        <v>61</v>
+      </c>
+      <c r="D138" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>14</v>
+      </c>
+      <c r="B139" t="s">
+        <v>23</v>
+      </c>
+      <c r="C139" t="s">
+        <v>61</v>
+      </c>
+      <c r="E139" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>16</v>
+      </c>
+      <c r="B141" t="s">
+        <v>28</v>
+      </c>
+      <c r="C141" t="s">
+        <v>61</v>
+      </c>
+      <c r="E141" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>17</v>
+      </c>
+      <c r="B142" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142" t="s">
+        <v>61</v>
+      </c>
+      <c r="D142" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>18</v>
+      </c>
+      <c r="B143" t="s">
+        <v>32</v>
+      </c>
+      <c r="C143" t="s">
+        <v>61</v>
+      </c>
+      <c r="D143" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>19</v>
+      </c>
+      <c r="B144" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144" t="s">
+        <v>61</v>
+      </c>
+      <c r="D144" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>20</v>
+      </c>
+      <c r="B145" t="s">
+        <v>36</v>
+      </c>
+      <c r="C145" t="s">
+        <v>61</v>
+      </c>
+      <c r="D145" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>21</v>
+      </c>
+      <c r="B146" t="s">
+        <v>37</v>
+      </c>
+      <c r="C146" t="s">
+        <v>61</v>
+      </c>
+      <c r="E146" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>22</v>
+      </c>
+      <c r="B147" t="s">
+        <v>39</v>
+      </c>
+      <c r="C147" t="s">
+        <v>61</v>
+      </c>
+      <c r="D147" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>23</v>
+      </c>
+      <c r="B148" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148" t="s">
+        <v>61</v>
+      </c>
+      <c r="D148" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>24</v>
+      </c>
+      <c r="B149" t="s">
+        <v>43</v>
+      </c>
+      <c r="C149" t="s">
+        <v>61</v>
+      </c>
+      <c r="D149" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>45</v>
+      </c>
+      <c r="C150" t="s">
+        <v>61</v>
+      </c>
+      <c r="D150" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>26</v>
+      </c>
+      <c r="B151" t="s">
+        <v>47</v>
+      </c>
+      <c r="C151" t="s">
+        <v>61</v>
+      </c>
+      <c r="D151" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>27</v>
+      </c>
+      <c r="B152" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" t="s">
+        <v>61</v>
+      </c>
+      <c r="D152" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>28</v>
+      </c>
+      <c r="B153" t="s">
+        <v>50</v>
+      </c>
+      <c r="C153" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>29</v>
+      </c>
+      <c r="B154" t="s">
+        <v>52</v>
+      </c>
+      <c r="C154" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>30</v>
+      </c>
+      <c r="B155" t="s">
+        <v>54</v>
+      </c>
+      <c r="C155" t="s">
+        <v>61</v>
+      </c>
+      <c r="D155" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>31</v>
+      </c>
+      <c r="B156" t="s">
+        <v>56</v>
+      </c>
+      <c r="C156" t="s">
+        <v>61</v>
+      </c>
+      <c r="D156" t="s">
+        <v>57</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>